--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294831</v>
+        <v>123294783</v>
       </c>
       <c r="B4" t="n">
-        <v>57358</v>
+        <v>57394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,16 +936,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,14 +982,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294845</v>
+        <v>123294834</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1130,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294758</v>
+        <v>123294797</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,39 +1148,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,11 +1226,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294834</v>
+        <v>123294788</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57386</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,20 +1264,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1292,14 +1285,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1340,9 +1333,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294838</v>
+        <v>123294831</v>
       </c>
       <c r="B8" t="n">
-        <v>56787</v>
+        <v>57358</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,28 +1384,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>100011</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1453,6 +1460,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294783</v>
+        <v>123294838</v>
       </c>
       <c r="B9" t="n">
-        <v>57394</v>
+        <v>56787</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,35 +1503,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>100038</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1560,24 +1572,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294797</v>
+        <v>123294758</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>57657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1613,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102623</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,6 +1699,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294788</v>
+        <v>123294845</v>
       </c>
       <c r="B11" t="n">
-        <v>57386</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1746,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100082</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1801,19 +1811,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294796</v>
+        <v>123294834</v>
       </c>
       <c r="B2" t="n">
-        <v>58183</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -752,19 +756,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294847</v>
+        <v>123294838</v>
       </c>
       <c r="B3" t="n">
-        <v>57913</v>
+        <v>56790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -904,7 +898,7 @@
         <v>123294783</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294834</v>
+        <v>123294758</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,20 +1032,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,12 +1053,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1107,9 +1105,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294797</v>
+        <v>123294847</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,27 +1165,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1213,19 +1230,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294788</v>
+        <v>123294796</v>
       </c>
       <c r="B7" t="n">
-        <v>57386</v>
+        <v>58186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,32 +1271,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100082</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1375,7 +1378,7 @@
         <v>123294831</v>
       </c>
       <c r="B8" t="n">
-        <v>57358</v>
+        <v>57361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1491,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294838</v>
+        <v>123294797</v>
       </c>
       <c r="B9" t="n">
-        <v>56787</v>
+        <v>57634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,35 +1506,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1572,9 +1571,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294758</v>
+        <v>123294788</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,16 +1626,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102623</v>
+        <v>100082</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1636,16 +1645,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1699,11 +1704,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,7 +1733,7 @@
         <v>123294845</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>57500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294834</v>
+        <v>123294796</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>58186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -756,9 +752,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294838</v>
+        <v>123294783</v>
       </c>
       <c r="B3" t="n">
-        <v>56790</v>
+        <v>57397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,9 +872,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294783</v>
+        <v>123294788</v>
       </c>
       <c r="B4" t="n">
-        <v>57397</v>
+        <v>57389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -991,11 +1012,6 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1149,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294847</v>
+        <v>123294834</v>
       </c>
       <c r="B6" t="n">
-        <v>57916</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1259,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294796</v>
+        <v>123294838</v>
       </c>
       <c r="B7" t="n">
-        <v>58186</v>
+        <v>56790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,20 +1287,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1311,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1336,19 +1356,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294831</v>
+        <v>123294845</v>
       </c>
       <c r="B8" t="n">
-        <v>57361</v>
+        <v>57500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,32 +1397,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100011</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1463,11 +1469,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294797</v>
+        <v>123294831</v>
       </c>
       <c r="B9" t="n">
-        <v>57634</v>
+        <v>57361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,27 +1511,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100011</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1571,19 +1580,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294788</v>
+        <v>123294797</v>
       </c>
       <c r="B10" t="n">
-        <v>57389</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,32 +1626,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100082</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294845</v>
+        <v>123294847</v>
       </c>
       <c r="B11" t="n">
-        <v>57500</v>
+        <v>57916</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,20 +1742,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294796</v>
+        <v>123294838</v>
       </c>
       <c r="B2" t="n">
-        <v>58186</v>
+        <v>56790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -752,19 +756,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294783</v>
+        <v>123294847</v>
       </c>
       <c r="B3" t="n">
-        <v>57397</v>
+        <v>57916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,24 +866,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294788</v>
+        <v>123294797</v>
       </c>
       <c r="B4" t="n">
-        <v>57389</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,32 +907,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -1165,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294834</v>
+        <v>123294796</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>58186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,31 +1156,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1246,9 +1217,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294838</v>
+        <v>123294783</v>
       </c>
       <c r="B7" t="n">
-        <v>56790</v>
+        <v>57397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,35 +1268,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1356,9 +1337,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1495,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294831</v>
+        <v>123294788</v>
       </c>
       <c r="B9" t="n">
-        <v>57361</v>
+        <v>57389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,20 +1503,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100011</v>
+        <v>100082</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,11 +1531,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1580,14 +1572,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294797</v>
+        <v>123294831</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>57361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,27 +1627,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100011</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,19 +1696,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294847</v>
+        <v>123294834</v>
       </c>
       <c r="B11" t="n">
-        <v>57916</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294788</v>
+        <v>123294796</v>
       </c>
       <c r="B2" t="n">
-        <v>57389</v>
+        <v>58192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100082</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294831</v>
+        <v>123294783</v>
       </c>
       <c r="B3" t="n">
-        <v>57361</v>
+        <v>57403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100011</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,16 +826,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,14 +872,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294797</v>
+        <v>123294845</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +928,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,19 +997,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294783</v>
+        <v>123294831</v>
       </c>
       <c r="B5" t="n">
-        <v>57397</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>100011</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,12 +1061,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1111,24 +1111,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294838</v>
+        <v>123294788</v>
       </c>
       <c r="B6" t="n">
-        <v>56790</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,31 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>100082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1236,9 +1226,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
         <v>123294758</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294796</v>
+        <v>123294797</v>
       </c>
       <c r="B8" t="n">
-        <v>58186</v>
+        <v>57640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294847</v>
+        <v>123294834</v>
       </c>
       <c r="B9" t="n">
-        <v>57916</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294834</v>
+        <v>123294847</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>57922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294845</v>
+        <v>123294838</v>
       </c>
       <c r="B11" t="n">
-        <v>57500</v>
+        <v>56796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>100038</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294796</v>
+        <v>123294838</v>
       </c>
       <c r="B2" t="n">
-        <v>58192</v>
+        <v>56799</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -752,19 +756,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294783</v>
+        <v>123294758</v>
       </c>
       <c r="B3" t="n">
-        <v>57403</v>
+        <v>57669</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,12 +820,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -889,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +917,7 @@
         <v>123294845</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294831</v>
+        <v>123294834</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1040,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100011</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,11 +1057,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1114,11 +1108,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294788</v>
+        <v>123294783</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,20 +1146,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100082</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1241,6 +1230,11 @@
           <t>15:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1265,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294758</v>
+        <v>123294831</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,20 +1271,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>100011</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1300,14 +1294,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1350,24 +1344,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294797</v>
+        <v>123294847</v>
       </c>
       <c r="B8" t="n">
-        <v>57640</v>
+        <v>57925</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,27 +1394,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1471,19 +1459,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294834</v>
+        <v>123294788</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>57398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,20 +1500,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1543,14 +1521,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1591,9 +1569,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294847</v>
+        <v>123294796</v>
       </c>
       <c r="B10" t="n">
-        <v>57922</v>
+        <v>58195</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,16 +1624,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1656,11 +1644,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1701,9 +1685,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294838</v>
+        <v>123294797</v>
       </c>
       <c r="B11" t="n">
-        <v>56796</v>
+        <v>57643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,35 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1811,9 +1801,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>123294758</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294845</v>
+        <v>123294834</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294834</v>
+        <v>123294797</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,31 +1040,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1105,9 +1101,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1143,7 @@
         <v>123294783</v>
       </c>
       <c r="B6" t="n">
-        <v>57406</v>
+        <v>57407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294831</v>
+        <v>123294845</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,32 +1277,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100011</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1347,11 +1349,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294847</v>
+        <v>123294831</v>
       </c>
       <c r="B8" t="n">
-        <v>57925</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,24 +1391,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>100011</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1462,6 +1463,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,7 +1497,7 @@
         <v>123294788</v>
       </c>
       <c r="B9" t="n">
-        <v>57398</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,7 +1617,7 @@
         <v>123294796</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1724,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294797</v>
+        <v>123294847</v>
       </c>
       <c r="B11" t="n">
-        <v>57643</v>
+        <v>57926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,27 +1746,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1801,19 +1811,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294758</v>
+        <v>123294834</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,16 +818,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -870,24 +866,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294834</v>
+        <v>123294758</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,12 +928,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -995,9 +980,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294845</v>
+        <v>123294831</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>57371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,28 +1277,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100011</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1349,6 +1353,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294831</v>
+        <v>123294845</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,32 +1396,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100011</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1463,11 +1468,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294834</v>
+        <v>123294758</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,12 +818,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -866,9 +870,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294758</v>
+        <v>123294834</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,20 +926,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,16 +947,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -980,24 +995,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294831</v>
+        <v>123294845</v>
       </c>
       <c r="B7" t="n">
-        <v>57371</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,32 +1277,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100011</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1353,11 +1349,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294845</v>
+        <v>123294831</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,28 +1387,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102977</v>
+        <v>100011</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1468,6 +1463,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294838</v>
+        <v>123294831</v>
       </c>
       <c r="B2" t="n">
-        <v>56799</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -759,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294758</v>
+        <v>123294834</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +806,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,16 +827,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -870,24 +875,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294834</v>
+        <v>123294845</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1140,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294783</v>
+        <v>123294758</v>
       </c>
       <c r="B6" t="n">
-        <v>57407</v>
+        <v>57670</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,20 +1142,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100067</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,12 +1165,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1238,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294845</v>
+        <v>123294783</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>57407</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,35 +1271,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102977</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,9 +1340,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294831</v>
+        <v>123294788</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,20 +1396,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100011</v>
+        <v>100082</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1415,11 +1424,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1460,14 +1465,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294788</v>
+        <v>123294838</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>56799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,31 +1520,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100082</v>
+        <v>100038</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1575,19 +1585,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294796</v>
+        <v>123294847</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>57926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,7 +1650,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,19 +1695,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294847</v>
+        <v>123294796</v>
       </c>
       <c r="B11" t="n">
-        <v>57926</v>
+        <v>58196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,16 +1740,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1766,11 +1760,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1811,9 +1801,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294834</v>
+        <v>123294838</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>56799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294845</v>
+        <v>123294758</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,29 +920,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -985,9 +989,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294797</v>
+        <v>123294845</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,31 +1045,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,19 +1114,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294758</v>
+        <v>123294783</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,20 +1155,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,16 +1178,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294783</v>
+        <v>123294797</v>
       </c>
       <c r="B7" t="n">
-        <v>57407</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,28 +1284,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1355,11 +1360,6 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294788</v>
+        <v>123294796</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>58196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,32 +1396,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100082</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1504,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294838</v>
+        <v>123294788</v>
       </c>
       <c r="B9" t="n">
-        <v>56799</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,31 +1516,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>100082</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1585,9 +1581,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294847</v>
+        <v>123294834</v>
       </c>
       <c r="B10" t="n">
-        <v>57926</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1724,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294796</v>
+        <v>123294847</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>57926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,16 +1746,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1760,7 +1766,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1801,19 +1811,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294831</v>
+        <v>123294845</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100011</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -763,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294838</v>
+        <v>123294797</v>
       </c>
       <c r="B3" t="n">
-        <v>56799</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,9 +862,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294758</v>
+        <v>123294847</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,37 +913,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -989,24 +982,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294845</v>
+        <v>123294796</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>58196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,11 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,9 +1088,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1268,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294797</v>
+        <v>123294831</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>57371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,27 +1268,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100011</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1345,19 +1337,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294796</v>
+        <v>123294788</v>
       </c>
       <c r="B8" t="n">
-        <v>58196</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,28 +1383,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>100082</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294788</v>
+        <v>123294758</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57670</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,16 +1507,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100082</v>
+        <v>102623</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,12 +1526,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1594,6 +1589,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294834</v>
+        <v>123294838</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>56799</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294847</v>
+        <v>123294834</v>
       </c>
       <c r="B11" t="n">
-        <v>57926</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294845</v>
+        <v>123294834</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123294797</v>
+        <v>123294838</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>56799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -862,19 +866,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294847</v>
+        <v>123294797</v>
       </c>
       <c r="B4" t="n">
-        <v>57926</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,31 +911,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,9 +972,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294796</v>
+        <v>123294845</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1047,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,19 +1092,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123294783</v>
+        <v>123294788</v>
       </c>
       <c r="B6" t="n">
-        <v>57407</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,20 +1133,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100067</v>
+        <v>100082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,7 +1156,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1223,11 +1217,6 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294788</v>
+        <v>123294783</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57407</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,20 +1372,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100082</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,7 +1395,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1467,6 +1456,11 @@
           <t>15:30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123294758</v>
+        <v>123294847</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,37 +1497,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102623</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1576,24 +1566,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294838</v>
+        <v>123294758</v>
       </c>
       <c r="B10" t="n">
-        <v>56799</v>
+        <v>57670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,29 +1611,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>102623</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1701,9 +1680,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123294834</v>
+        <v>123294796</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>58196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,31 +1740,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1811,9 +1801,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123294834</v>
+        <v>123294831</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,7 +703,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -759,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +792,7 @@
         <v>123294838</v>
       </c>
       <c r="B3" t="n">
-        <v>56799</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,43 +894,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123294797</v>
+        <v>123294834</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,19 +970,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123294845</v>
+        <v>123294783</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,31 +1010,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1092,9 +1075,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,12 +1122,7 @@
         <v>123294788</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,32 +1234,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123294831</v>
+        <v>123294758</v>
       </c>
       <c r="B7" t="n">
-        <v>57371</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100011</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,14 +1264,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1326,14 +1314,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kl 13:50-13.52, sågs rakt från sidan så något osäker på ålder.</t>
+          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,47 +1358,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123294783</v>
+        <v>123294845</v>
       </c>
       <c r="B8" t="n">
-        <v>57407</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1441,24 +1434,9 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ad långt i nordväst 11:40, 2 ad i par kretsande i öster 13:15, 1 ej åldersbestämd på hög höjd i norr 14:20 samt 1 2k mot SV i nordvästlig riktning 14.35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,12 +1466,7 @@
         <v>123294847</v>
       </c>
       <c r="B9" t="n">
-        <v>57926</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,51 +1568,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123294758</v>
+        <v>123294797</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102623</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,11 +1653,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sjöng ungefär hela dagen, sågs även väl</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,12 +1682,7 @@
         <v>123294796</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 50985-2021 artfynd.xlsx
+++ b/artfynd/A 50985-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294834</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294783</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294788</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294845</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294847</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294797</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,8 +1837,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123294796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>